--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B4" t="n">
-        <v>96320</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R4" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B5" t="n">
-        <v>58097</v>
+        <v>96320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,31 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R5" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S5" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>96323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R4" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S4" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B5" t="n">
-        <v>96320</v>
+        <v>58097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,31 +1018,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R5" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,48 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B2" t="n">
-        <v>95963</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R2" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +751,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,68 +778,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>95963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R3" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,19 +858,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B4" t="n">
-        <v>96323</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R4" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B5" t="n">
-        <v>58097</v>
+        <v>96323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,31 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R5" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S5" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>95963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R2" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S2" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +743,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,60 +760,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B3" t="n">
-        <v>95963</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R3" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,9 +848,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>96323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R4" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S4" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B5" t="n">
-        <v>96323</v>
+        <v>58097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,31 +1018,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R5" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,48 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B2" t="n">
-        <v>95963</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R2" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +751,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,68 +778,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>95963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R3" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,19 +858,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>95963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R2" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S2" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +743,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,60 +760,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B3" t="n">
-        <v>95963</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R3" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,9 +848,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129533188</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B4" t="n">
-        <v>96323</v>
+        <v>58100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R4" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B5" t="n">
-        <v>58097</v>
+        <v>96352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,31 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R5" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S5" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
         <v>129537906</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129533188</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>58100</v>
+        <v>96364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R4" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S4" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B5" t="n">
-        <v>96352</v>
+        <v>58105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,31 +1018,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R5" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
         <v>129537906</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129533188</v>
       </c>
       <c r="B3" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129533189</v>
       </c>
       <c r="B5" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129537906</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,48 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B2" t="n">
-        <v>96010</v>
+        <v>57894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R2" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +751,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,68 +778,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B3" t="n">
-        <v>57894</v>
+        <v>96010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R3" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,19 +858,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>57894</v>
+        <v>96010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R2" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S2" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +743,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,60 +760,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B3" t="n">
-        <v>96010</v>
+        <v>57894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R3" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,9 +848,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B4" t="n">
-        <v>96370</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R4" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>96370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,31 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R5" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S5" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>96370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R4" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S4" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +975,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
+        <v>58106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,31 +1018,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R5" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129537908</v>
       </c>
       <c r="B4" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129537908</v>
+        <v>129533189</v>
       </c>
       <c r="B4" t="n">
-        <v>96376</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462137</v>
+        <v>462267</v>
       </c>
       <c r="R4" t="n">
-        <v>6255108</v>
+        <v>6255218</v>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129533189</v>
+        <v>129537908</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>96386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,31 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462267</v>
+        <v>462137</v>
       </c>
       <c r="R5" t="n">
-        <v>6255218</v>
+        <v>6255108</v>
       </c>
       <c r="S5" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,48 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B2" t="n">
-        <v>96026</v>
+        <v>57894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R2" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +751,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,68 +778,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B3" t="n">
-        <v>57894</v>
+        <v>96026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R3" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,19 +858,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 43639-2025 artfynd.xlsx
+++ b/artfynd/A 43639-2025 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129533188</v>
+        <v>129544723</v>
       </c>
       <c r="B2" t="n">
-        <v>57894</v>
+        <v>96030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringahallen, Sk</t>
+          <t>Käringahallen, Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462267</v>
+        <v>462148</v>
       </c>
       <c r="R2" t="n">
-        <v>6255218</v>
+        <v>6255056</v>
       </c>
       <c r="S2" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +743,9 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,60 +760,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129544723</v>
+        <v>129533188</v>
       </c>
       <c r="B3" t="n">
-        <v>96026</v>
+        <v>57893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringahallen, Käringahallen, Sk</t>
+          <t>Käringahallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462148</v>
+        <v>462267</v>
       </c>
       <c r="R3" t="n">
-        <v>6255056</v>
+        <v>6255218</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,9 +848,19 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -890,7 +890,7 @@
         <v>129533189</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>129537908</v>
       </c>
       <c r="B5" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129537906</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129544739</v>
       </c>
       <c r="B7" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
